--- a/data/trans_orig/IP04D$colectiva-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87929</t>
+          <t>87840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80612</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85533</t>
+          <t>85534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171260</t>
+          <t>171569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177247</t>
+          <t>177268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>16706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33716</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429871</t>
+          <t>429603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441329</t>
+          <t>441341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475208</t>
+          <t>474630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486748</t>
+          <t>486860</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908559</t>
+          <t>908840</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925458</t>
+          <t>925569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>26485</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150187</t>
+          <t>149393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160614</t>
+          <t>160591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158155</t>
+          <t>158769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168011</t>
+          <t>167820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312485</t>
+          <t>312556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326208</t>
+          <t>326783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30790</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57105</t>
+          <t>58761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673894</t>
+          <t>675357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>690310</t>
+          <t>690852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>720794</t>
+          <t>721526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737216</t>
+          <t>737336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1402771</t>
+          <t>1401115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1424110</t>
+          <t>1424143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54447</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123541</t>
+          <t>123624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26637</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453463</t>
+          <t>453744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>464431</t>
+          <t>464580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472809</t>
+          <t>472736</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482382</t>
+          <t>482376</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930243</t>
+          <t>930909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944220</t>
+          <t>944883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26777</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40869</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151174</t>
+          <t>151650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162698</t>
+          <t>162801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158533</t>
+          <t>158022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>172606</t>
+          <t>172480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315078</t>
+          <t>313432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>333242</t>
+          <t>332248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>666314</t>
+          <t>665729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>682789</t>
+          <t>682158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704301</t>
+          <t>704642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720629</t>
+          <t>721497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1376083</t>
+          <t>1376526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400081</t>
+          <t>1400092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4897</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50033</t>
+          <t>49991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111785</t>
+          <t>111450</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116266</t>
+          <t>116234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>18015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37146</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41716</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65211</t>
+          <t>67094</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427366</t>
+          <t>426252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443591</t>
+          <t>442495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>478766</t>
+          <t>479021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496290</t>
+          <t>496204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>911211</t>
+          <t>909328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934706</t>
+          <t>934805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33920</t>
+          <t>34028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40273</t>
+          <t>40340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62464</t>
+          <t>62989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112970</t>
+          <t>113470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130094</t>
+          <t>129438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148485</t>
+          <t>148377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164786</t>
+          <t>164607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268493</t>
+          <t>267968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290684</t>
+          <t>290617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41768</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>64878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>65804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88361</t>
+          <t>88707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123121</t>
+          <t>123730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598481</t>
+          <t>598861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621971</t>
+          <t>622796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694359</t>
+          <t>694518</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718019</t>
+          <t>719246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1300939</t>
+          <t>1300330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1335699</t>
+          <t>1335353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$colectiva-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5593</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1265</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4529</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3946</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5962</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80599</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>85526</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91104</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87840</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88423</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80230</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>85534</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>250</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171569</t>
+          <t>171140</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177268</t>
+          <t>177282</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11094</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6399</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18436</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12727</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7770</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19508</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7702</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18856</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6303</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18533</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>482069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>474727</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>486764</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>436384</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>429603</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>441341</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>430255</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>441409</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,17%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>482069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>474630</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>486860</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>908840</t>
+          <t>908610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925569</t>
+          <t>924950</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7821</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13712</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10810</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6221</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17419</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7821</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4408</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13459</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26485</t>
+          <t>27410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>164407</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158516</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>168056</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>156002</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149393</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>160591</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150062</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>160661</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>164407</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>158769</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>167820</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>312556</t>
+          <t>311631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>326783</t>
+          <t>326027</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14672</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>30313</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24802</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17440</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32935</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18213</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33912</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14248</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>30058</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58761</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>730612</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>721271</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>736912</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>986</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>683490</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>675357</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>690852</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>674380</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>690079</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>730612</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>721526</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>737336</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1401115</t>
+          <t>1400780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1424143</t>
+          <t>1423559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3724</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3282</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3740</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57997</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55026</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>55468</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,72%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>122797</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7378</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13276</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10866</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6213</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17049</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6760</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18679</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7378</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13351</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11997</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>26555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>478709</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>472811</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>482374</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>459927</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>453744</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>464580</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>452114</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>464033</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>478709</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>472736</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>482376</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930909</t>
+          <t>930325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944883</t>
+          <t>944364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18830</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13263</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27142</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12657</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7837</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18988</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19675</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,42%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18830</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12830</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>27288</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42515</t>
+          <t>41435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166480</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158168</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>172047</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,84%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>157981</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151650</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>162801</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>150963</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>162767</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166480</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>158022</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>172480</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313432</t>
+          <t>314512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>332248</t>
+          <t>331937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26208</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19093</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35833</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>24276</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18023</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34452</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>17194</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32882</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18514</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35369</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40100</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>62323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3472,67 +3472,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>713803</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>704178</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720918</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>675905</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>665729</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>682158</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>667299</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>682987</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>713803</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>704642</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721497</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1376526</t>
+          <t>1377869</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400092</t>
+          <t>1401378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1768</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4687</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>356</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56375</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54964</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53346</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49991</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>45326</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41623</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61577</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59812</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>149</t>
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>114924</t>
+          <t>101701</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>98233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116234</t>
+          <t>103134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25156</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18089</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34275</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24914</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18015</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34258</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27470</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>33618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41617</t>
+          <t>39707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67094</t>
+          <t>60888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>449906</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>440787</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>456973</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>601</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>435596</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>426252</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>442495</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>488442</t>
+          <t>407172</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479021</t>
+          <t>398830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496204</t>
+          <t>414503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>924038</t>
+          <t>857079</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>909328</t>
+          <t>846622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934805</t>
+          <t>867803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22039</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15371</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29659</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25879</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19114</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35082</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50746</t>
+          <t>48255</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40340</t>
+          <t>37522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62989</t>
+          <t>59915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>145423</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137803</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>152091</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>122673</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113470</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>129438</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>157539</t>
+          <t>122684</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148377</t>
+          <t>114576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>164607</t>
+          <t>129648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>280211</t>
+          <t>268107</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267968</t>
+          <t>256447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>290617</t>
+          <t>278840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47551</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37489</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59236</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>40943</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>64878</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65804</t>
+          <t>66072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>100475</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88707</t>
+          <t>85585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123730</t>
+          <t>117575</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>651705</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>640020</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>661767</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>859</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>611614</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>598861</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>622796</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,15%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>707559</t>
+          <t>575182</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694518</t>
+          <t>562034</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719246</t>
+          <t>584763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1319172</t>
+          <t>1226887</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1300330</t>
+          <t>1209787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1335353</t>
+          <t>1241777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
